--- a/output/yearly_total_coral_cover_iteration_92_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_92_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.282630240925454</v>
+        <v>1.252068434892251</v>
       </c>
       <c r="C3" t="n">
-        <v>4.582235633049739</v>
+        <v>4.603863534974296</v>
       </c>
       <c r="D3" t="n">
-        <v>6.124530063369421</v>
+        <v>6.088892621705262</v>
       </c>
       <c r="E3" t="n">
-        <v>11.98939593734461</v>
+        <v>11.94482459157181</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.450600453727908</v>
+        <v>1.370841108423839</v>
       </c>
       <c r="C4" t="n">
-        <v>5.007421751751323</v>
+        <v>5.033389788283571</v>
       </c>
       <c r="D4" t="n">
-        <v>6.439602489892028</v>
+        <v>6.334468028910823</v>
       </c>
       <c r="E4" t="n">
-        <v>12.89762469537126</v>
+        <v>12.73869892561823</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.678663091857008</v>
+        <v>1.532510118637984</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522883796751153</v>
+        <v>5.56066347478716</v>
       </c>
       <c r="D5" t="n">
-        <v>6.814713266562642</v>
+        <v>6.616035393002512</v>
       </c>
       <c r="E5" t="n">
-        <v>14.0162601551708</v>
+        <v>13.70920898642766</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.933151882512649</v>
+        <v>1.722738626963741</v>
       </c>
       <c r="C6" t="n">
-        <v>6.172471913507922</v>
+        <v>6.195463844714348</v>
       </c>
       <c r="D6" t="n">
-        <v>7.182360864184795</v>
+        <v>6.99330712774868</v>
       </c>
       <c r="E6" t="n">
-        <v>15.28798466020537</v>
+        <v>14.91150959942677</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.221185776902712</v>
+        <v>1.943587448924708</v>
       </c>
       <c r="C7" t="n">
-        <v>6.939977409631738</v>
+        <v>6.933982722890882</v>
       </c>
       <c r="D7" t="n">
-        <v>7.53164113919964</v>
+        <v>7.518390131401061</v>
       </c>
       <c r="E7" t="n">
-        <v>16.69280432573409</v>
+        <v>16.39596030321665</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.42077137197945</v>
+        <v>1.193965072355311</v>
       </c>
       <c r="C8" t="n">
-        <v>4.617726128881511</v>
+        <v>4.59884685736327</v>
       </c>
       <c r="D8" t="n">
-        <v>5.87320685415826</v>
+        <v>5.793226568690013</v>
       </c>
       <c r="E8" t="n">
-        <v>11.91170435501922</v>
+        <v>11.58603849840859</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.816840149065882</v>
+        <v>1.513872762265269</v>
       </c>
       <c r="C9" t="n">
-        <v>5.546490284038391</v>
+        <v>5.623317249982762</v>
       </c>
       <c r="D9" t="n">
-        <v>6.446711003960286</v>
+        <v>6.415976125282917</v>
       </c>
       <c r="E9" t="n">
-        <v>13.81004143706456</v>
+        <v>13.55316613753095</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.245186447370826</v>
+        <v>1.846926374290976</v>
       </c>
       <c r="C10" t="n">
-        <v>6.594166211345754</v>
+        <v>6.833880652335172</v>
       </c>
       <c r="D10" t="n">
-        <v>7.041023982616495</v>
+        <v>6.995388049948013</v>
       </c>
       <c r="E10" t="n">
-        <v>15.88037664133308</v>
+        <v>15.67619507657416</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.688831289247085</v>
+        <v>2.17794533137755</v>
       </c>
       <c r="C11" t="n">
-        <v>7.72490930037908</v>
+        <v>8.203386841427287</v>
       </c>
       <c r="D11" t="n">
-        <v>7.626475047501153</v>
+        <v>7.681107163136471</v>
       </c>
       <c r="E11" t="n">
-        <v>18.04021563712732</v>
+        <v>18.06243933594131</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.165547649409704</v>
+        <v>2.509943286387207</v>
       </c>
       <c r="C12" t="n">
-        <v>8.94739425839972</v>
+        <v>9.736089476253602</v>
       </c>
       <c r="D12" t="n">
-        <v>8.230141161021271</v>
+        <v>8.33165495287451</v>
       </c>
       <c r="E12" t="n">
-        <v>20.34308306883069</v>
+        <v>20.57768771551532</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.640610954904147</v>
+        <v>2.818692986992381</v>
       </c>
       <c r="C13" t="n">
-        <v>10.21536114225696</v>
+        <v>11.3200421916879</v>
       </c>
       <c r="D13" t="n">
-        <v>8.761958919240916</v>
+        <v>8.971995686952516</v>
       </c>
       <c r="E13" t="n">
-        <v>22.61793101640202</v>
+        <v>23.1107308656328</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.098937321771511</v>
+        <v>1.626088357498077</v>
       </c>
       <c r="C14" t="n">
-        <v>7.263931628768065</v>
+        <v>7.968914837710657</v>
       </c>
       <c r="D14" t="n">
-        <v>6.652675873149915</v>
+        <v>6.840955447870369</v>
       </c>
       <c r="E14" t="n">
-        <v>16.01554482368949</v>
+        <v>16.4359586430791</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.21146524363228</v>
+        <v>1.649002348915197</v>
       </c>
       <c r="C15" t="n">
-        <v>7.735170526806534</v>
+        <v>8.74613504273173</v>
       </c>
       <c r="D15" t="n">
-        <v>6.717755928464437</v>
+        <v>6.979234612013532</v>
       </c>
       <c r="E15" t="n">
-        <v>16.66439169890325</v>
+        <v>17.37437200366046</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.618851270986537</v>
+        <v>1.895666459607209</v>
       </c>
       <c r="C16" t="n">
-        <v>9.100015820204534</v>
+        <v>10.44000326173101</v>
       </c>
       <c r="D16" t="n">
-        <v>7.307737211331558</v>
+        <v>7.517742862746992</v>
       </c>
       <c r="E16" t="n">
-        <v>19.02660430252263</v>
+        <v>19.85341258408521</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.136577528752334</v>
+        <v>1.507218345467873</v>
       </c>
       <c r="C17" t="n">
-        <v>8.417779705569341</v>
+        <v>9.782860618416363</v>
       </c>
       <c r="D17" t="n">
-        <v>6.8582538424192</v>
+        <v>7.042449346689985</v>
       </c>
       <c r="E17" t="n">
-        <v>17.41261107674087</v>
+        <v>18.33252831057422</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.477214529694849</v>
+        <v>1.704529999067397</v>
       </c>
       <c r="C18" t="n">
-        <v>9.823573695711477</v>
+        <v>11.44744330339796</v>
       </c>
       <c r="D18" t="n">
-        <v>7.37676389241715</v>
+        <v>7.531585505376874</v>
       </c>
       <c r="E18" t="n">
-        <v>19.67755211782348</v>
+        <v>20.68355880784223</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.518114139053772</v>
+        <v>1.697333788395268</v>
       </c>
       <c r="C19" t="n">
-        <v>10.53194393423372</v>
+        <v>12.2802991508187</v>
       </c>
       <c r="D19" t="n">
-        <v>7.525302320069693</v>
+        <v>7.678494231840365</v>
       </c>
       <c r="E19" t="n">
-        <v>20.57536039335719</v>
+        <v>21.65612717105433</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.840068481184471</v>
+        <v>1.885711537886146</v>
       </c>
       <c r="C20" t="n">
-        <v>12.15923984140802</v>
+        <v>14.1029137637529</v>
       </c>
       <c r="D20" t="n">
-        <v>8.019229407553306</v>
+        <v>8.271332400526845</v>
       </c>
       <c r="E20" t="n">
-        <v>23.01853773014579</v>
+        <v>24.25995770216589</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.705433206955305</v>
+        <v>1.121411132652962</v>
       </c>
       <c r="C21" t="n">
-        <v>9.047629762705926</v>
+        <v>10.33192265697047</v>
       </c>
       <c r="D21" t="n">
-        <v>6.705169922895993</v>
+        <v>6.955545039910057</v>
       </c>
       <c r="E21" t="n">
-        <v>17.45823289255722</v>
+        <v>18.40887882953349</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_92_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_92_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.252068434892251</v>
+        <v>1.287077558025692</v>
       </c>
       <c r="C3" t="n">
-        <v>4.603863534974296</v>
+        <v>4.593555184079705</v>
       </c>
       <c r="D3" t="n">
-        <v>6.088892621705262</v>
+        <v>6.047659218126895</v>
       </c>
       <c r="E3" t="n">
-        <v>11.94482459157181</v>
+        <v>11.92829196023229</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.370841108423839</v>
+        <v>1.460909486222144</v>
       </c>
       <c r="C4" t="n">
-        <v>5.033389788283571</v>
+        <v>5.028878817458319</v>
       </c>
       <c r="D4" t="n">
-        <v>6.334468028910823</v>
+        <v>6.324749061157686</v>
       </c>
       <c r="E4" t="n">
-        <v>12.73869892561823</v>
+        <v>12.81453736483815</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.532510118637984</v>
+        <v>1.693525150617226</v>
       </c>
       <c r="C5" t="n">
-        <v>5.56066347478716</v>
+        <v>5.571625869613229</v>
       </c>
       <c r="D5" t="n">
-        <v>6.616035393002512</v>
+        <v>6.565698824738133</v>
       </c>
       <c r="E5" t="n">
-        <v>13.70920898642766</v>
+        <v>13.83084984496859</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.722738626963741</v>
+        <v>1.954708975348266</v>
       </c>
       <c r="C6" t="n">
-        <v>6.195463844714348</v>
+        <v>6.26392567269666</v>
       </c>
       <c r="D6" t="n">
-        <v>6.99330712774868</v>
+        <v>6.988927469739858</v>
       </c>
       <c r="E6" t="n">
-        <v>14.91150959942677</v>
+        <v>15.20756211778478</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.943587448924708</v>
+        <v>2.238827212499522</v>
       </c>
       <c r="C7" t="n">
-        <v>6.933982722890882</v>
+        <v>7.06534006366846</v>
       </c>
       <c r="D7" t="n">
-        <v>7.518390131401061</v>
+        <v>7.302603389899114</v>
       </c>
       <c r="E7" t="n">
-        <v>16.39596030321665</v>
+        <v>16.6067706660671</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.193965072355311</v>
+        <v>1.422304227706046</v>
       </c>
       <c r="C8" t="n">
-        <v>4.59884685736327</v>
+        <v>4.708751512065939</v>
       </c>
       <c r="D8" t="n">
-        <v>5.793226568690013</v>
+        <v>5.531137498548522</v>
       </c>
       <c r="E8" t="n">
-        <v>11.58603849840859</v>
+        <v>11.66219323832051</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.513872762265269</v>
+        <v>1.810356465224997</v>
       </c>
       <c r="C9" t="n">
-        <v>5.623317249982762</v>
+        <v>5.694413055807304</v>
       </c>
       <c r="D9" t="n">
-        <v>6.415976125282917</v>
+        <v>6.035523209806476</v>
       </c>
       <c r="E9" t="n">
-        <v>13.55316613753095</v>
+        <v>13.54029273083878</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.846926374290976</v>
+        <v>2.231806444076487</v>
       </c>
       <c r="C10" t="n">
-        <v>6.833880652335172</v>
+        <v>6.797830050840298</v>
       </c>
       <c r="D10" t="n">
-        <v>6.995388049948013</v>
+        <v>6.610371752586135</v>
       </c>
       <c r="E10" t="n">
-        <v>15.67619507657416</v>
+        <v>15.64000824750292</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.17794533137755</v>
+        <v>2.659558855855555</v>
       </c>
       <c r="C11" t="n">
-        <v>8.203386841427287</v>
+        <v>7.974032951185391</v>
       </c>
       <c r="D11" t="n">
-        <v>7.681107163136471</v>
+        <v>7.161850686608904</v>
       </c>
       <c r="E11" t="n">
-        <v>18.06243933594131</v>
+        <v>17.79544249364985</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.509943286387207</v>
+        <v>3.111556482551912</v>
       </c>
       <c r="C12" t="n">
-        <v>9.736089476253602</v>
+        <v>9.219864289296112</v>
       </c>
       <c r="D12" t="n">
-        <v>8.33165495287451</v>
+        <v>7.657820352340496</v>
       </c>
       <c r="E12" t="n">
-        <v>20.57768771551532</v>
+        <v>19.98924112418852</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.818692986992381</v>
+        <v>3.549371717589749</v>
       </c>
       <c r="C13" t="n">
-        <v>11.3200421916879</v>
+        <v>10.49481896195511</v>
       </c>
       <c r="D13" t="n">
-        <v>8.971995686952516</v>
+        <v>8.172150575671182</v>
       </c>
       <c r="E13" t="n">
-        <v>23.1107308656328</v>
+        <v>22.21634125521604</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.626088357498077</v>
+        <v>2.052382845636127</v>
       </c>
       <c r="C14" t="n">
-        <v>7.968914837710657</v>
+        <v>7.42211081887631</v>
       </c>
       <c r="D14" t="n">
-        <v>6.840955447870369</v>
+        <v>6.244985504007343</v>
       </c>
       <c r="E14" t="n">
-        <v>16.4359586430791</v>
+        <v>15.71947916851978</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.649002348915197</v>
+        <v>2.138796278563931</v>
       </c>
       <c r="C15" t="n">
-        <v>8.74613504273173</v>
+        <v>7.844959372572455</v>
       </c>
       <c r="D15" t="n">
-        <v>6.979234612013532</v>
+        <v>6.301494901863789</v>
       </c>
       <c r="E15" t="n">
-        <v>17.37437200366046</v>
+        <v>16.28525055300017</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.895666459607209</v>
+        <v>2.518644282814065</v>
       </c>
       <c r="C16" t="n">
-        <v>10.44000326173101</v>
+        <v>9.166951378680084</v>
       </c>
       <c r="D16" t="n">
-        <v>7.517742862746992</v>
+        <v>6.801371380435138</v>
       </c>
       <c r="E16" t="n">
-        <v>19.85341258408521</v>
+        <v>18.48696704192929</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.507218345467873</v>
+        <v>2.042231574374215</v>
       </c>
       <c r="C17" t="n">
-        <v>9.782860618416363</v>
+        <v>8.403161482253106</v>
       </c>
       <c r="D17" t="n">
-        <v>7.042449346689985</v>
+        <v>6.350169953040345</v>
       </c>
       <c r="E17" t="n">
-        <v>18.33252831057422</v>
+        <v>16.79556300966767</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.704529999067397</v>
+        <v>2.370282569748287</v>
       </c>
       <c r="C18" t="n">
-        <v>11.44744330339796</v>
+        <v>9.777254839025112</v>
       </c>
       <c r="D18" t="n">
-        <v>7.531585505376874</v>
+        <v>6.795382719439234</v>
       </c>
       <c r="E18" t="n">
-        <v>20.68355880784223</v>
+        <v>18.94292012821263</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.697333788395268</v>
+        <v>2.416493434187184</v>
       </c>
       <c r="C19" t="n">
-        <v>12.2802991508187</v>
+        <v>10.45274634693213</v>
       </c>
       <c r="D19" t="n">
-        <v>7.678494231840365</v>
+        <v>6.919622891411667</v>
       </c>
       <c r="E19" t="n">
-        <v>21.65612717105433</v>
+        <v>19.78886267253098</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.885711537886146</v>
+        <v>2.73958660365481</v>
       </c>
       <c r="C20" t="n">
-        <v>14.1029137637529</v>
+        <v>12.05833581236553</v>
       </c>
       <c r="D20" t="n">
-        <v>8.271332400526845</v>
+        <v>7.35544033228091</v>
       </c>
       <c r="E20" t="n">
-        <v>24.25995770216589</v>
+        <v>22.15336274830125</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.121411132652962</v>
+        <v>1.657975522932014</v>
       </c>
       <c r="C21" t="n">
-        <v>10.33192265697047</v>
+        <v>8.961775925969542</v>
       </c>
       <c r="D21" t="n">
-        <v>6.955545039910057</v>
+        <v>6.142167066941576</v>
       </c>
       <c r="E21" t="n">
-        <v>18.40887882953349</v>
+        <v>16.76191851584313</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_92_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_92_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.287077558025692</v>
+        <v>2.576812356174218</v>
       </c>
       <c r="C3" t="n">
-        <v>4.593555184079705</v>
+        <v>7.69928481757282</v>
       </c>
       <c r="D3" t="n">
-        <v>6.047659218126895</v>
+        <v>8.21398632217921</v>
       </c>
       <c r="E3" t="n">
-        <v>11.92829196023229</v>
+        <v>18.49008349592625</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.460909486222144</v>
+        <v>1.039711076509537</v>
       </c>
       <c r="C4" t="n">
-        <v>5.028878817458319</v>
+        <v>4.465523773401961</v>
       </c>
       <c r="D4" t="n">
-        <v>6.324749061157686</v>
+        <v>5.764812767713828</v>
       </c>
       <c r="E4" t="n">
-        <v>12.81453736483815</v>
+        <v>11.27004761762533</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.693525150617226</v>
+        <v>1.105887981282327</v>
       </c>
       <c r="C5" t="n">
-        <v>5.571625869613229</v>
+        <v>5.065513742967308</v>
       </c>
       <c r="D5" t="n">
-        <v>6.565698824738133</v>
+        <v>6.025450922501689</v>
       </c>
       <c r="E5" t="n">
-        <v>13.83084984496859</v>
+        <v>12.19685264675132</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.954708975348266</v>
+        <v>1.180461658646446</v>
       </c>
       <c r="C6" t="n">
-        <v>6.26392567269666</v>
+        <v>5.865068091164289</v>
       </c>
       <c r="D6" t="n">
-        <v>6.988927469739858</v>
+        <v>6.328415793757583</v>
       </c>
       <c r="E6" t="n">
-        <v>15.20756211778478</v>
+        <v>13.37394554356832</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.238827212499522</v>
+        <v>1.257579390611532</v>
       </c>
       <c r="C7" t="n">
-        <v>7.06534006366846</v>
+        <v>6.854725845958809</v>
       </c>
       <c r="D7" t="n">
-        <v>7.302603389899114</v>
+        <v>6.652618487127097</v>
       </c>
       <c r="E7" t="n">
-        <v>16.6067706660671</v>
+        <v>14.76492372369744</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.422304227706046</v>
+        <v>1.333360044996593</v>
       </c>
       <c r="C8" t="n">
-        <v>4.708751512065939</v>
+        <v>8.082873106118017</v>
       </c>
       <c r="D8" t="n">
-        <v>5.531137498548522</v>
+        <v>7.02148397458424</v>
       </c>
       <c r="E8" t="n">
-        <v>11.66219323832051</v>
+        <v>16.43771712569885</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.810356465224997</v>
+        <v>1.408125615816956</v>
       </c>
       <c r="C9" t="n">
-        <v>5.694413055807304</v>
+        <v>9.504333712516308</v>
       </c>
       <c r="D9" t="n">
-        <v>6.035523209806476</v>
+        <v>7.479808124276962</v>
       </c>
       <c r="E9" t="n">
-        <v>13.54029273083878</v>
+        <v>18.39226745261023</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.231806444076487</v>
+        <v>0.9072723234026473</v>
       </c>
       <c r="C10" t="n">
-        <v>6.797830050840298</v>
+        <v>7.094511427446193</v>
       </c>
       <c r="D10" t="n">
-        <v>6.610371752586135</v>
+        <v>5.888944881585195</v>
       </c>
       <c r="E10" t="n">
-        <v>15.64000824750292</v>
+        <v>13.89072863243404</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.659558855855555</v>
+        <v>0.8101676579755953</v>
       </c>
       <c r="C11" t="n">
-        <v>7.974032951185391</v>
+        <v>7.735965742446974</v>
       </c>
       <c r="D11" t="n">
-        <v>7.161850686608904</v>
+        <v>5.737274678756105</v>
       </c>
       <c r="E11" t="n">
-        <v>17.79544249364985</v>
+        <v>14.28340807917867</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.111556482551912</v>
+        <v>0.8429285788663113</v>
       </c>
       <c r="C12" t="n">
-        <v>9.219864289296112</v>
+        <v>9.322617294665456</v>
       </c>
       <c r="D12" t="n">
-        <v>7.657820352340496</v>
+        <v>6.097419006582006</v>
       </c>
       <c r="E12" t="n">
-        <v>19.98924112418852</v>
+        <v>16.26296488011377</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.549371717589749</v>
+        <v>0.654374114788669</v>
       </c>
       <c r="C13" t="n">
-        <v>10.49481896195511</v>
+        <v>9.018324593734159</v>
       </c>
       <c r="D13" t="n">
-        <v>8.172150575671182</v>
+        <v>5.555101574756067</v>
       </c>
       <c r="E13" t="n">
-        <v>22.21634125521604</v>
+        <v>15.2278002832789</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.052382845636127</v>
+        <v>0.6877142668248907</v>
       </c>
       <c r="C14" t="n">
-        <v>7.42211081887631</v>
+        <v>10.70556601572977</v>
       </c>
       <c r="D14" t="n">
-        <v>6.244985504007343</v>
+        <v>5.8927835151088</v>
       </c>
       <c r="E14" t="n">
-        <v>15.71947916851978</v>
+        <v>17.28606379766346</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.138796278563931</v>
+        <v>0.6482872790223387</v>
       </c>
       <c r="C15" t="n">
-        <v>7.844959372572455</v>
+        <v>11.68093235989897</v>
       </c>
       <c r="D15" t="n">
-        <v>6.301494901863789</v>
+        <v>5.925416808797963</v>
       </c>
       <c r="E15" t="n">
-        <v>16.28525055300017</v>
+        <v>18.25463644771928</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.518644282814065</v>
+        <v>0.6925248305757</v>
       </c>
       <c r="C16" t="n">
-        <v>9.166951378680084</v>
+        <v>13.68740868288452</v>
       </c>
       <c r="D16" t="n">
-        <v>6.801371380435138</v>
+        <v>6.331379301981062</v>
       </c>
       <c r="E16" t="n">
-        <v>18.48696704192929</v>
+        <v>20.71131281544128</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.042231574374215</v>
+        <v>0.4174194888916589</v>
       </c>
       <c r="C17" t="n">
-        <v>8.403161482253106</v>
+        <v>10.23644769273247</v>
       </c>
       <c r="D17" t="n">
-        <v>6.350169953040345</v>
+        <v>5.25161390694225</v>
       </c>
       <c r="E17" t="n">
-        <v>16.79556300966767</v>
+        <v>15.90548108856638</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.370282569748287</v>
+        <v>0.3092897967459152</v>
       </c>
       <c r="C18" t="n">
-        <v>9.777254839025112</v>
+        <v>9.221408923834653</v>
       </c>
       <c r="D18" t="n">
-        <v>6.795382719439234</v>
+        <v>4.769713228835661</v>
       </c>
       <c r="E18" t="n">
-        <v>18.94292012821263</v>
+        <v>14.30041194941623</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.416493434187184</v>
+        <v>0.354754532929585</v>
       </c>
       <c r="C19" t="n">
-        <v>10.45274634693213</v>
+        <v>11.44917117935743</v>
       </c>
       <c r="D19" t="n">
-        <v>6.919622891411667</v>
+        <v>5.212933047394927</v>
       </c>
       <c r="E19" t="n">
-        <v>19.78886267253098</v>
+        <v>17.01685875968194</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.73958660365481</v>
+        <v>0.3928954312395735</v>
       </c>
       <c r="C20" t="n">
-        <v>12.05833581236553</v>
+        <v>13.82019987736094</v>
       </c>
       <c r="D20" t="n">
-        <v>7.35544033228091</v>
+        <v>5.617687990901801</v>
       </c>
       <c r="E20" t="n">
-        <v>22.15336274830125</v>
+        <v>19.83078329950232</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.657975522932014</v>
+        <v>0.4275707601535709</v>
       </c>
       <c r="C21" t="n">
-        <v>8.961775925969542</v>
+        <v>16.28786200189347</v>
       </c>
       <c r="D21" t="n">
-        <v>6.142167066941576</v>
+        <v>6.033536683466665</v>
       </c>
       <c r="E21" t="n">
-        <v>16.76191851584313</v>
+        <v>22.74896944551371</v>
       </c>
     </row>
   </sheetData>
